--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_2_4.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_2_4.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="195" windowWidth="14805" windowHeight="7920"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14355" windowHeight="4920"/>
   </bookViews>
   <sheets>
     <sheet name="表2-4资产收益权按基础资产投向" sheetId="4" r:id="rId1"/>
@@ -16,7 +16,7 @@
     <definedName name="Err">[1]综合校验!$B$2</definedName>
     <definedName name="Thd">[1]综合校验!$B$1</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -144,9 +144,6 @@
   </si>
   <si>
     <t>列编号</t>
-  </si>
-  <si>
-    <t>单位：万元</t>
   </si>
   <si>
     <t>01-银行非保本理财</t>
@@ -175,6 +172,7 @@
         <b/>
         <sz val="16"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>4 资产收益权按基础资产投向分类统计模板</t>
@@ -381,6 +379,10 @@
   </si>
   <si>
     <t>${report.enddate}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：万元</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -391,7 +393,7 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="179" formatCode="#,##0.000000_ "/>
+    <numFmt numFmtId="178" formatCode="#,##0.000000_ "/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -404,37 +406,44 @@
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -454,12 +463,14 @@
       <b/>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -559,7 +570,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -645,7 +656,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -696,8 +707,47 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -707,42 +757,6 @@
     </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -755,6 +769,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -849,7 +866,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -891,7 +908,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -926,7 +943,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1150,19 +1167,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A1" s="57" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
+      <c r="A1" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
     </row>
     <row r="2" spans="1:11" s="9" customFormat="1" ht="24.95" customHeight="1">
       <c r="A2" s="28"/>
@@ -1170,10 +1187,10 @@
       <c r="C2" s="27"/>
       <c r="D2" s="22"/>
       <c r="E2" s="29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G2" s="28"/>
       <c r="H2" s="27"/>
@@ -1183,54 +1200,54 @@
     </row>
     <row r="3" spans="1:11" s="9" customFormat="1" ht="24.95" customHeight="1">
       <c r="A3" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="25"/>
       <c r="C3" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="56"/>
+      <c r="F3" s="57" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="58" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="59"/>
-      <c r="F3" s="60" t="s">
+      <c r="G3" s="58"/>
+      <c r="H3" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="59"/>
+      <c r="J3" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="G3" s="61"/>
-      <c r="H3" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" s="62"/>
-      <c r="J3" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="K3" s="63"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" s="2" customFormat="1" ht="24.95" customHeight="1" thickBot="1">
       <c r="A4" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="64"/>
+      <c r="B4" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="61"/>
       <c r="D4" s="42"/>
       <c r="E4" s="43"/>
       <c r="F4" s="44"/>
       <c r="G4" s="45"/>
       <c r="H4" s="46"/>
       <c r="I4" s="47"/>
-      <c r="J4" s="65" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" s="65"/>
+      <c r="J4" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="K4" s="63"/>
     </row>
     <row r="5" spans="1:11" s="2" customFormat="1" ht="18" customHeight="1">
       <c r="A5" s="36"/>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="51"/>
+      <c r="C5" s="64"/>
       <c r="D5" s="37" t="s">
         <v>35</v>
       </c>
@@ -1260,10 +1277,10 @@
       <c r="A6" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="52"/>
+      <c r="C6" s="65"/>
       <c r="D6" s="31" t="s">
         <v>25</v>
       </c>
@@ -1293,256 +1310,256 @@
       <c r="A7" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="53"/>
+      <c r="C7" s="66"/>
       <c r="D7" s="33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I7" s="33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="19" customFormat="1" ht="18" customHeight="1">
       <c r="A8" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="51" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="35" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H8" s="33" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I8" s="33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J8" s="33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K8" s="33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="19" customFormat="1" ht="18" customHeight="1">
       <c r="A9" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="54"/>
+      <c r="B9" s="51"/>
       <c r="C9" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H9" s="33" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I9" s="33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J9" s="33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K9" s="33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="19" customFormat="1" ht="18" customHeight="1">
       <c r="A10" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="54"/>
+      <c r="B10" s="51"/>
       <c r="C10" s="35" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H10" s="33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I10" s="33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J10" s="33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K10" s="33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="19" customFormat="1" ht="18" customHeight="1">
       <c r="A11" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="54"/>
+      <c r="B11" s="51"/>
       <c r="C11" s="35" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H11" s="33" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I11" s="33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J11" s="33" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K11" s="33" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="19" customFormat="1" ht="18" customHeight="1">
       <c r="A12" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="54"/>
+      <c r="B12" s="51"/>
       <c r="C12" s="35" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H12" s="33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I12" s="33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J12" s="33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K12" s="33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
       <c r="A13" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="55"/>
+      <c r="B13" s="52"/>
       <c r="C13" s="49" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E13" s="50" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F13" s="50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G13" s="50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H13" s="50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I13" s="50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J13" s="50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K13" s="50" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="6" customFormat="1" ht="72.75" customHeight="1">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="56"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="56"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="53"/>
     </row>
     <row r="15" spans="1:11" s="9" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="15" t="s">
         <v>2</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="15"/>
@@ -1550,7 +1567,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G15" s="14"/>
       <c r="H15" s="10"/>
@@ -1559,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="6" customFormat="1">
@@ -1575,11 +1592,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:B13"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A1:K1"/>
@@ -1587,6 +1599,11 @@
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="J3:K3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
